--- a/Student_analysis_40.0.xlsx
+++ b/Student_analysis_40.0.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Exceeding Expectation</t>
+          <t>Approaching Expectation</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Exceeding Expectation</t>
+          <t>Meeting Expectation</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Exceeding Expectation</t>
+          <t>Meeting Expectation</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Exceeding Expectation</t>
+          <t>Meeting Expectation</t>
         </is>
       </c>
     </row>
